--- a/test_data/Treaties OtherArticles/Treaties OtherArticles_Test_Cases.xlsx
+++ b/test_data/Treaties OtherArticles/Treaties OtherArticles_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -803,6 +803,606 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking an article-reference link opens the treaty article modal</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the 'Art. 4(4)' link in the Austria row's 'Tie Breaker Corporate' column must open a modal titled 'Treaty between Australia and Austria' showing the Article 4(4) text.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected on Other Articles.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria, column: Tie Breaker Corporate</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Other Articles
+2. Select Australia
+3. Click the 'Art. 4(4)' link in the Austria row
+4. Verify the article modal title and content</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the 'Art. 4(4)' link in the Austria row's 'Tie Breaker Corporate' column must open a modal titled 'Treaty between Australia and Austria' showing the Article 4(4) text.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the Austria article link correctly opened the modal ('Treaty between Australia and Austria\nFull DTA').</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The article modal opens with the correct treaty title and article text</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>The article modal's PDF export downloads a real, non-empty file</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected, Austria's article modal open.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Other Articles, select Australia
+2. Open the Austria article modal
+3. Click 'PDF' under Export
+4. Verify a real, non-empty PDF download completed</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>PDF export downloaded 'AU_AT_Art. 4(4)_Treaty_Article.pdf' (17727 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The PDF export downloads a real, non-empty .pdf file with no failure</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>The article modal's Word export downloads a real, non-empty file</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'Word' under Export must trigger a real file download with no failure and a non-zero size.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected, Austria's article modal open.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Other Articles, select Australia
+2. Open the Austria article modal
+3. Click 'Word' under Export
+4. Verify a real, non-empty Word download completed</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'Word' under Export must trigger a real file download with no failure and a non-zero size.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Word export downloaded 'AU_AT_Art. 4(4)_Treaty_Article.doc' (8364 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The Word export downloads a real, non-empty .doc(x) file with no failure</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>The article modal's Print action opens a print-preview tab with the expected content</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'Print' under Export must open a NEW browser tab showing a print-preview rendering of the treaty name and article text. The test verifies the preview content and closes the tab - it never clicks any actual 'Print' confirmation control.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected, Austria's article modal open.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Other Articles, select Australia
+2. Open the Austria article modal
+3. Click 'Print' under Export
+4. Verify the new print-preview tab shows the treaty name and article text, then close it</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'Print' under Export must open a NEW browser tab showing a print-preview rendering of the treaty name and article text. The test verifies the preview content and closes the tab - it never clicks any actual 'Print' confirmation control.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>The Print action correctly opened a print-preview tab with the expected treaty/article content (no Print confirmation control was clicked).</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The print-preview tab shows the treaty name and Article 4(4) text</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>The article modal's 'Full DTA' link swaps in the full document viewer</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking the 'Full DTA' link in the modal header must swap the modal's content for the full DTA document viewer - a 'Contents' sidebar listing every treaty article.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected, Austria's article modal open.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Other Articles, select Australia
+2. Open the Austria article modal
+3. Click the 'Full DTA' link
+4. Verify the 'Contents' sidebar with article entries is shown</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking the 'Full DTA' link in the modal header must swap the modal's content for the full DTA document viewer - a 'Contents' sidebar listing every treaty article.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>The 'Full DTA' link correctly opened the full document viewer (32 article entries).</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The 'Full DTA' link swaps in the full document viewer with a populated Contents sidebar</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>The article modal's header X button closes it</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking the header X close button must dismiss the modal.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected, Austria's article modal open.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Other Articles, select Australia
+2. Open the Austria article modal
+3. Click the header X close button
+4. Verify the modal is no longer visible</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking the header X close button must dismiss the modal.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>The header X button correctly closed the article modal.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The article modal is no longer visible after clicking the X close button</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>The table-level 'Export as Excel' button downloads the whole table</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected (no article link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected on Other Articles.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Other Articles
+2. Select Australia
+3. Click the 'Export as Excel' icon button
+4. Verify a real, non-empty .xlsx download completed</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected (no article link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Table export downloaded 'AU_OtherArticles.xlsx' (4290 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Exporting the table downloads a real, non-empty .xlsx file with no failure</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Article link + PDF export work correctly for a second country (Canada)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>With Canada selected, clicking the Algeria row's Tie Breaker Corporate article link must open the correctly-titled modal, and its PDF export must download a real, non-empty file - confirming the behavior is not Australia-specific.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Other Articles.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Country: Canada, partner: Algeria</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Other Articles
+2. Select Canada
+3. Click the Algeria row's article link and verify the modal title
+4. Click 'PDF' under Export and verify a real download</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>With Canada selected, clicking the Algeria row's Tie Breaker Corporate article link must open the correctly-titled modal, and its PDF export must download a real, non-empty file - confirming the behavior is not Australia-specific.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Canada's article link/modal/PDF export all worked correctly ('CA_DZ_Art. 4(3)_Treaty_Article.pdf', 18287 bytes).</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Canada's article modal and PDF export both work correctly</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Article link + PDF export work correctly for a third country (Germany)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>With Germany selected, clicking the Albania row's Tie Breaker Corporate article link must open the correctly-titled modal, and its PDF export must download a real, non-empty file - confirming the behavior generalizes across countries.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Other Articles.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Country: Germany, partner: Albania</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Other Articles
+2. Select Germany
+3. Click the Albania row's article link and verify the modal title
+4. Click 'PDF' under Export and verify a real download</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>With Germany selected, clicking the Albania row's Tie Breaker Corporate article link must open the correctly-titled modal, and its PDF export must download a real, non-empty file - confirming the behavior generalizes across countries.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Germany's article link/modal/PDF export all worked correctly ('DE_AL_Art. 4 (3)_Treaty_Article.pdf', 17979 bytes).</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Germany's article modal and PDF export both work correctly</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>A cell with no treaty article coverage ('None') has no clickable link</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, Belgium's 'Other Income' cell shows plain 'None' text with no linked article - clicking it must not open any modal. This is the genuine negative case for the article-link feature.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected on Other Articles.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Belgium, column: Other Income</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Other Articles
+2. Select Australia
+3. Verify Belgium's 'Other Income' cell has no '.reg-link-button' article link
+4. Verify no article modal opens</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, Belgium's 'Other Income' cell shows plain 'None' text with no linked article - clicking it must not open any modal. This is the genuine negative case for the article-link feature.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Belgium's 'Other Income' cell correctly shows plain 'None' text with no clickable article link (genuine no-coverage case).</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Belgium's 'Other Income' cell shows plain 'None' text with no clickable article link</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test_data/Treaties OtherArticles/Treaties OtherArticles_Test_Cases.xlsx
+++ b/test_data/Treaties OtherArticles/Treaties OtherArticles_Test_Cases.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Other Articles loaded correctly at https://regplus.kaz.com.bd/wta/OtherArticles.</t>
+          <t>Other Articles loaded correctly at https://regplusrc.reganalytics.com/wta/OtherArticles.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Selecting Australia rendered the Other Articles table with the expected headers and 43 rows.</t>
+          <t>Selecting Australia rendered the Other Articles table with the expected headers and 45 rows.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Word export downloaded 'AU_AT_Art. 4(4)_Treaty_Article.doc' (8364 bytes) successfully.</t>
+          <t>Word export downloaded 'AU_AT_Art. 4(4)_Treaty_Article.doc' (8363 bytes) successfully.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>The 'Full DTA' link correctly opened the full document viewer (32 article entries).</t>
+          <t>The 'Full DTA' link correctly opened the full document viewer (29 article entries).</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Table export downloaded 'AU_OtherArticles.xlsx' (4290 bytes) successfully.</t>
+          <t>Table export downloaded 'AU_OtherArticles.xlsx' (4347 bytes) successfully.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
